--- a/香港現在上映電影 2025-06-15.xlsx
+++ b/香港現在上映電影 2025-06-15.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.spyder-py3\utility\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F86CA53-53CD-4B47-9B0F-AED1D9A5AAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="138">
   <si>
     <t>英文名稱</t>
   </si>
@@ -52,7 +46,10 @@
     <t>全球票房</t>
   </si>
   <si>
-    <t>超時空武士</t>
+    <t>乘著光的幻想</t>
+  </si>
+  <si>
+    <t>破．地獄</t>
   </si>
   <si>
     <t>黑箱日誌</t>
@@ -70,10 +67,7 @@
     <t>哪咤之魔童鬧海</t>
   </si>
   <si>
-    <t>日麗</t>
-  </si>
-  <si>
-    <t>陽光燦爛的果園</t>
+    <t>布達佩斯大酒店</t>
   </si>
   <si>
     <t>死神來了：血脈</t>
@@ -112,7 +106,10 @@
     <t>拿坡里的美麗傳說</t>
   </si>
   <si>
-    <t>A SAMURAI IN TIME</t>
+    <t>All We Imagine as Light</t>
+  </si>
+  <si>
+    <t>The Last Dance</t>
   </si>
   <si>
     <t>Black Box Diaries</t>
@@ -130,10 +127,7 @@
     <t>Ne Zha 2</t>
   </si>
   <si>
-    <t>Aftersun</t>
-  </si>
-  <si>
-    <t>Alcarras</t>
+    <t>The Grand Budapest Hotel</t>
   </si>
   <si>
     <t>Final Destination: Bloodlines</t>
@@ -172,7 +166,10 @@
     <t>Parthenope</t>
   </si>
   <si>
-    <t>9/5/2025</t>
+    <t>26/9/2024</t>
+  </si>
+  <si>
+    <t>9/11/2024</t>
   </si>
   <si>
     <t>3/4/2024</t>
@@ -190,10 +187,7 @@
     <t>22/2/2025</t>
   </si>
   <si>
-    <t>11/5/2023</t>
-  </si>
-  <si>
-    <t>14/3/2023</t>
+    <t>26/2/2014</t>
   </si>
   <si>
     <t>29/5/2025</t>
@@ -217,7 +211,7 @@
     <t>19/10/2024</t>
   </si>
   <si>
-    <t>喜劇、劇情、科幻</t>
+    <t>劇情</t>
   </si>
   <si>
     <t>紀錄片</t>
@@ -235,7 +229,7 @@
     <t>奇幻、劇情、動畫、冒險</t>
   </si>
   <si>
-    <t>劇情</t>
+    <t>喜劇、劇情</t>
   </si>
   <si>
     <t>恐怖</t>
@@ -271,7 +265,10 @@
     <t>浪漫、劇情、奇幻</t>
   </si>
   <si>
-    <t>2h 11m</t>
+    <t>1h 58m</t>
+  </si>
+  <si>
+    <t>2h 6m</t>
   </si>
   <si>
     <t>1h 43m</t>
@@ -289,27 +286,24 @@
     <t>2h 23m</t>
   </si>
   <si>
+    <t>1h 39m</t>
+  </si>
+  <si>
+    <t>1h 50m</t>
+  </si>
+  <si>
+    <t>1h 44m</t>
+  </si>
+  <si>
+    <t>1h 35m</t>
+  </si>
+  <si>
+    <t>2h 49m</t>
+  </si>
+  <si>
     <t>1h 41m</t>
   </si>
   <si>
-    <t>2h 0m</t>
-  </si>
-  <si>
-    <t>1h 50m</t>
-  </si>
-  <si>
-    <t>1h 44m</t>
-  </si>
-  <si>
-    <t>2h 6m</t>
-  </si>
-  <si>
-    <t>1h 35m</t>
-  </si>
-  <si>
-    <t>2h 49m</t>
-  </si>
-  <si>
     <t>2h 5m</t>
   </si>
   <si>
@@ -322,22 +316,28 @@
     <t>2h 16m</t>
   </si>
   <si>
+    <t>IIB</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
     <t>IIA</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>IIB</t>
-  </si>
-  <si>
-    <t>III</t>
+    <t>2102萬</t>
+  </si>
+  <si>
+    <t>2.383億</t>
   </si>
   <si>
     <t>27.38萬</t>
   </si>
   <si>
-    <t>28.20億</t>
+    <t>28.35億</t>
   </si>
   <si>
     <t>2.400億</t>
@@ -346,40 +346,37 @@
     <t>3.378億</t>
   </si>
   <si>
-    <t>7654萬</t>
-  </si>
-  <si>
-    <t>2536萬</t>
-  </si>
-  <si>
-    <t>20.83億</t>
-  </si>
-  <si>
-    <t>1.275億</t>
-  </si>
-  <si>
-    <t>29.66億</t>
-  </si>
-  <si>
-    <t>36.07億</t>
+    <t>12.80億</t>
+  </si>
+  <si>
+    <t>21.33億</t>
+  </si>
+  <si>
+    <t>1.553億</t>
+  </si>
+  <si>
+    <t>29.75億</t>
+  </si>
+  <si>
+    <t>39.78億</t>
   </si>
   <si>
     <t>1.820億</t>
   </si>
   <si>
-    <t>1.718億</t>
-  </si>
-  <si>
-    <t>1.233億</t>
-  </si>
-  <si>
-    <t>4.593億</t>
-  </si>
-  <si>
-    <t>63.62億</t>
-  </si>
-  <si>
-    <t>6.102億</t>
+    <t>2.113億</t>
+  </si>
+  <si>
+    <t>15.53億</t>
+  </si>
+  <si>
+    <t>7.185億</t>
+  </si>
+  <si>
+    <t>64.83億</t>
+  </si>
+  <si>
+    <t>7.061億</t>
   </si>
   <si>
     <t>7962萬</t>
@@ -395,12 +392,6 @@
   </si>
   <si>
     <t>96</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>93</t>
   </si>
   <si>
     <t>92</t>
@@ -442,12 +433,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -467,7 +458,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -484,28 +475,6 @@
       <color rgb="FF0000FF"/>
       <name val="CALIBRI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="8"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -540,11 +509,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -561,31 +529,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="超連結" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -623,7 +579,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -657,7 +613,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -692,10 +647,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -868,19 +822,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="41.703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.29296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.29296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.703125" style="1" customWidth="1"/>
-    <col min="6" max="11" width="15.703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="41.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
@@ -912,7 +871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -929,19 +888,25 @@
         <v>83</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G2" s="1">
-        <v>7</v>
+        <v>149</v>
+      </c>
+      <c r="H2" s="1">
+        <v>70</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K2" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -952,7 +917,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>84</v>
@@ -961,22 +926,22 @@
         <v>122</v>
       </c>
       <c r="G3" s="1">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I3" s="1">
         <v>50</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -987,7 +952,7 @@
         <v>52</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>85</v>
@@ -996,22 +961,22 @@
         <v>123</v>
       </c>
       <c r="G4" s="1">
-        <v>371</v>
+        <v>67</v>
       </c>
       <c r="H4" s="1">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I4" s="1">
-        <v>25000</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1022,31 +987,31 @@
         <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G5" s="1">
-        <v>182</v>
+        <v>371</v>
       </c>
       <c r="H5" s="1">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1">
-        <v>500</v>
+        <v>25000</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1057,7 +1022,7 @@
         <v>54</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>87</v>
@@ -1066,65 +1031,68 @@
         <v>124</v>
       </c>
       <c r="G6" s="1">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="H6" s="1">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G7" s="1">
-        <v>23</v>
+        <v>267</v>
       </c>
       <c r="H7" s="1">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="I7" s="1">
         <v>1000</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>89</v>
@@ -1133,22 +1101,19 @@
         <v>125</v>
       </c>
       <c r="G8" s="1">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="H8" s="1">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1">
         <v>1000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1168,22 +1133,22 @@
         <v>126</v>
       </c>
       <c r="G9" s="1">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="H9" s="1">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I9" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1191,7 +1156,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>72</v>
@@ -1200,7 +1165,7 @@
         <v>91</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G10" s="1">
         <v>209</v>
@@ -1212,13 +1177,13 @@
         <v>5000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1235,7 +1200,7 @@
         <v>92</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="1">
         <v>181</v>
@@ -1247,13 +1212,13 @@
         <v>1000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1267,10 +1232,10 @@
         <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G12" s="1">
         <v>345</v>
@@ -1282,13 +1247,13 @@
         <v>10000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -1302,19 +1267,19 @@
         <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13" s="1">
         <v>17</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1328,10 +1293,10 @@
         <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G14" s="1">
         <v>388</v>
@@ -1343,13 +1308,13 @@
         <v>10000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1363,10 +1328,10 @@
         <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G15" s="1">
         <v>134</v>
@@ -1378,13 +1343,13 @@
         <v>1000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -1398,10 +1363,10 @@
         <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G16" s="1">
         <v>240</v>
@@ -1413,13 +1378,13 @@
         <v>1000</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -1427,7 +1392,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>78</v>
@@ -1436,10 +1401,10 @@
         <v>96</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G17" s="1">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H17" s="1">
         <v>98</v>
@@ -1448,13 +1413,13 @@
         <v>2500</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -1471,7 +1436,7 @@
         <v>96</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G18" s="1">
         <v>258</v>
@@ -1483,13 +1448,13 @@
         <v>2500</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
@@ -1506,10 +1471,10 @@
         <v>97</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G19" s="1">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H19" s="1">
         <v>93</v>
@@ -1521,10 +1486,10 @@
         <v>101</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
@@ -1541,7 +1506,7 @@
         <v>98</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G20" s="1">
         <v>170</v>
@@ -1553,13 +1518,13 @@
         <v>2500</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1541,7 @@
         <v>99</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G21" s="1">
         <v>96</v>
@@ -1588,92 +1553,91 @@
         <v>100</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="A3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="K3" r:id="rId7" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="A4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B4" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F4" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K4" r:id="rId11" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A5" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B5" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F5" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K5" r:id="rId15" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B6" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F6" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="K6" r:id="rId19" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A7" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F7" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="A8" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B8" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F8" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K8" r:id="rId25" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A9" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B9" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F9" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K9" r:id="rId29" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="A10" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B10" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F10" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K10" r:id="rId33" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="A11" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B11" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F11" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K11" r:id="rId37" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="A12" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B12" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F12" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K12" r:id="rId41" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="A13" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B13" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F13" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="A14" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B14" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F14" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K14" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="A15" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B15" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F15" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K15" r:id="rId52" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="A16" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B16" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F16" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K16" r:id="rId56" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="A17" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B17" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F17" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K17" r:id="rId60" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="A18" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B18" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F18" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="K18" r:id="rId64" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="A19" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B19" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F19" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="K19" r:id="rId68" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="A20" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B20" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F20" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="K20" r:id="rId72" location="tab=summary" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="A21" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B21" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F21" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="K21" r:id="rId76" location="tab=summary" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B7" r:id="rId77" xr:uid="{E2EB28DD-E01B-4E80-AD0B-B2AA481F145A}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="F2" r:id="rId3"/>
+    <hyperlink ref="K2" r:id="rId4" location="tab=summary"/>
+    <hyperlink ref="A3" r:id="rId5"/>
+    <hyperlink ref="B3" r:id="rId6"/>
+    <hyperlink ref="F3" r:id="rId7"/>
+    <hyperlink ref="K3" r:id="rId8" location="tab=summary"/>
+    <hyperlink ref="A4" r:id="rId9"/>
+    <hyperlink ref="B4" r:id="rId10"/>
+    <hyperlink ref="F4" r:id="rId11"/>
+    <hyperlink ref="K4" r:id="rId12" location="tab=summary"/>
+    <hyperlink ref="A5" r:id="rId13"/>
+    <hyperlink ref="B5" r:id="rId14"/>
+    <hyperlink ref="F5" r:id="rId15"/>
+    <hyperlink ref="K5" r:id="rId16" location="tab=summary"/>
+    <hyperlink ref="A6" r:id="rId17"/>
+    <hyperlink ref="B6" r:id="rId18"/>
+    <hyperlink ref="F6" r:id="rId19"/>
+    <hyperlink ref="K6" r:id="rId20" location="tab=summary"/>
+    <hyperlink ref="A7" r:id="rId21"/>
+    <hyperlink ref="B7" r:id="rId22"/>
+    <hyperlink ref="F7" r:id="rId23"/>
+    <hyperlink ref="K7" r:id="rId24" location="tab=summary"/>
+    <hyperlink ref="A8" r:id="rId25"/>
+    <hyperlink ref="F8" r:id="rId26"/>
+    <hyperlink ref="A9" r:id="rId27"/>
+    <hyperlink ref="B9" r:id="rId28"/>
+    <hyperlink ref="F9" r:id="rId29"/>
+    <hyperlink ref="K9" r:id="rId30" location="tab=summary"/>
+    <hyperlink ref="A10" r:id="rId31"/>
+    <hyperlink ref="B10" r:id="rId32"/>
+    <hyperlink ref="F10" r:id="rId33"/>
+    <hyperlink ref="K10" r:id="rId34" location="tab=summary"/>
+    <hyperlink ref="A11" r:id="rId35"/>
+    <hyperlink ref="B11" r:id="rId36"/>
+    <hyperlink ref="F11" r:id="rId37"/>
+    <hyperlink ref="K11" r:id="rId38" location="tab=summary"/>
+    <hyperlink ref="A12" r:id="rId39"/>
+    <hyperlink ref="B12" r:id="rId40"/>
+    <hyperlink ref="F12" r:id="rId41"/>
+    <hyperlink ref="K12" r:id="rId42" location="tab=summary"/>
+    <hyperlink ref="A13" r:id="rId43"/>
+    <hyperlink ref="B13" r:id="rId44"/>
+    <hyperlink ref="F13" r:id="rId45"/>
+    <hyperlink ref="A14" r:id="rId46"/>
+    <hyperlink ref="B14" r:id="rId47"/>
+    <hyperlink ref="F14" r:id="rId48"/>
+    <hyperlink ref="K14" r:id="rId49"/>
+    <hyperlink ref="A15" r:id="rId50"/>
+    <hyperlink ref="B15" r:id="rId51"/>
+    <hyperlink ref="F15" r:id="rId52"/>
+    <hyperlink ref="K15" r:id="rId53" location="tab=summary"/>
+    <hyperlink ref="A16" r:id="rId54"/>
+    <hyperlink ref="B16" r:id="rId55"/>
+    <hyperlink ref="F16" r:id="rId56"/>
+    <hyperlink ref="K16" r:id="rId57" location="tab=summary"/>
+    <hyperlink ref="A17" r:id="rId58"/>
+    <hyperlink ref="B17" r:id="rId59"/>
+    <hyperlink ref="F17" r:id="rId60"/>
+    <hyperlink ref="K17" r:id="rId61" location="tab=summary"/>
+    <hyperlink ref="A18" r:id="rId62"/>
+    <hyperlink ref="B18" r:id="rId63"/>
+    <hyperlink ref="F18" r:id="rId64"/>
+    <hyperlink ref="K18" r:id="rId65" location="tab=summary"/>
+    <hyperlink ref="A19" r:id="rId66"/>
+    <hyperlink ref="B19" r:id="rId67"/>
+    <hyperlink ref="F19" r:id="rId68"/>
+    <hyperlink ref="K19" r:id="rId69" location="tab=summary"/>
+    <hyperlink ref="A20" r:id="rId70"/>
+    <hyperlink ref="B20" r:id="rId71"/>
+    <hyperlink ref="F20" r:id="rId72"/>
+    <hyperlink ref="K20" r:id="rId73" location="tab=summary"/>
+    <hyperlink ref="A21" r:id="rId74"/>
+    <hyperlink ref="B21" r:id="rId75"/>
+    <hyperlink ref="F21" r:id="rId76"/>
+    <hyperlink ref="K21" r:id="rId77" location="tab=summary"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
